--- a/data/google-spreadsheet/M3GIM-Ortsindex.xlsx
+++ b/data/google-spreadsheet/M3GIM-Ortsindex.xlsx
@@ -13,10 +13,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={52a3fbbe-f931-4f1e-96aa-da2205c4fbde}</author>
+    <author>tc={ea664975-9bda-4530-8de1-11f97e375586}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{52a3fbbe-f931-4f1e-96aa-da2205c4fbde}" ref="B28">
+    <comment authorId="0" xr:uid="{ea664975-9bda-4530-8de1-11f97e375586}" ref="B28">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -30,7 +30,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="75">
+  <si>
+    <t>Turin</t>
+  </si>
   <si>
     <t>name</t>
   </si>
@@ -231,6 +234,27 @@
   </si>
   <si>
     <t>Bloomington, Indiana</t>
+  </si>
+  <si>
+    <t>L33</t>
+  </si>
+  <si>
+    <t>Wuppertal</t>
+  </si>
+  <si>
+    <t>Dresden</t>
+  </si>
+  <si>
+    <t>Belgrad</t>
+  </si>
+  <si>
+    <t>Düsseldorf</t>
+  </si>
+  <si>
+    <t>Brüssel</t>
+  </si>
+  <si>
+    <t>Ottobeuren</t>
   </si>
 </sst>
 </file>
@@ -311,10 +335,10 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -326,10 +350,10 @@
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -353,7 +377,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Digital Humanities Craft" id="{22ff0a97-516d-4304-9da8-fe38dc08796e}" providerId="google-sheets"/>
+  <x18tc:person displayName="Digital Humanities Craft" id="{09921612-882d-49b4-803c-dfcdc1a5184f}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -553,7 +577,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="B28" dT="2026-02-20T05:43:51.00" personId="{22ff0a97-516d-4304-9da8-fe38dc08796e}" id="{52a3fbbe-f931-4f1e-96aa-da2205c4fbde}" done="0">
+  <x18tc:threadedComment ref="B28" dT="2026-02-20T05:43:51.00" personId="{09921612-882d-49b4-803c-dfcdc1a5184f}" id="{ea664975-9bda-4530-8de1-11f97e375586}" done="0">
     <x18tc:text xml:space="preserve">doppelung</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -575,22 +599,24 @@
   </cols>
   <sheetData>
     <row r="1" ht="24.75" customHeight="1">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -598,117 +624,117 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
@@ -716,148 +742,179 @@
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="B35" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="B36" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="B37" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="B38" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
     <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="B40" s="5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="B41" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
     <row r="42" ht="15.75" customHeight="1"/>
     <row r="43" ht="15.75" customHeight="1"/>
     <row r="44" ht="15.75" customHeight="1"/>
